--- a/data/trans_orig/P64D1_R-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P64D1_R-Provincia-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>33260</t>
+          <t>38832</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22730</t>
+          <t>28006</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47062</t>
+          <t>53299</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>13,97%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>26,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>39295</t>
+          <t>41370</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>30656</t>
+          <t>33268</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49463</t>
+          <t>50588</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>34,27%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>72555</t>
+          <t>80202</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56922</t>
+          <t>65947</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88628</t>
+          <t>97183</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>18,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>26,34%</t>
+          <t>27,51%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>158908</t>
+          <t>161675</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>145106</t>
+          <t>147208</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>169438</t>
+          <t>172501</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>80,63%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,17%</t>
+          <t>86,03%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>105037</t>
+          <t>111387</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>94869</t>
+          <t>102169</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>113676</t>
+          <t>119489</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,92%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>66,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>263946</t>
+          <t>273061</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>247873</t>
+          <t>256080</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>279579</t>
+          <t>287316</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>73,66%</t>
+          <t>72,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>83,08%</t>
+          <t>81,33%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>192168</t>
+          <t>200507</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>192168</t>
+          <t>200507</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>192168</t>
+          <t>200507</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>144332</t>
+          <t>152757</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>336501</t>
+          <t>353263</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>336501</t>
+          <t>353263</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>336501</t>
+          <t>353263</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>50145</t>
+          <t>55714</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35234</t>
+          <t>38329</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>69573</t>
+          <t>72873</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>49745</t>
+          <t>55514</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>39342</t>
+          <t>45947</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60047</t>
+          <t>67167</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>31,99%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>36,25%</t>
+          <t>38,7%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>99890</t>
+          <t>111228</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>80286</t>
+          <t>92840</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>121067</t>
+          <t>133384</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>25,98%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>31,15%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>195430</t>
+          <t>198856</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>176002</t>
+          <t>181697</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>210341</t>
+          <t>216241</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,67%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>84,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>115888</t>
+          <t>118047</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>105586</t>
+          <t>106394</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126291</t>
+          <t>127614</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>69,97%</t>
+          <t>68,01%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,75%</t>
+          <t>61,3%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>73,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>311318</t>
+          <t>316903</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>290141</t>
+          <t>294747</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>330922</t>
+          <t>335291</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>75,71%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>68,85%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>78,32%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>245575</t>
+          <t>254570</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>245575</t>
+          <t>254570</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>245575</t>
+          <t>254570</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>165633</t>
+          <t>173561</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>165633</t>
+          <t>173561</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>165633</t>
+          <t>173561</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>411208</t>
+          <t>428131</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>411208</t>
+          <t>428131</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>411208</t>
+          <t>428131</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39309</t>
+          <t>38783</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29980</t>
+          <t>29507</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51324</t>
+          <t>49489</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51720</t>
+          <t>53980</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42598</t>
+          <t>44660</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61780</t>
+          <t>63701</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>42,79%</t>
+          <t>43,88%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,25%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>91029</t>
+          <t>92763</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76898</t>
+          <t>79484</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>106860</t>
+          <t>107378</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>28,53%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,38%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>109373</t>
+          <t>110828</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>97358</t>
+          <t>100122</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>118702</t>
+          <t>120104</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>73,56%</t>
+          <t>74,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>66,92%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>69142</t>
+          <t>69049</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>59082</t>
+          <t>59328</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78264</t>
+          <t>78369</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>57,21%</t>
+          <t>56,12%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,75%</t>
+          <t>63,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>178514</t>
+          <t>179877</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>162683</t>
+          <t>165262</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192645</t>
+          <t>193156</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>71,47%</t>
+          <t>70,85%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>148682</t>
+          <t>149611</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>120862</t>
+          <t>123029</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>269543</t>
+          <t>272640</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>38430</t>
+          <t>55400</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>27939</t>
+          <t>39537</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>53806</t>
+          <t>75167</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,69%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>35,82%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>124223</t>
+          <t>62881</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>65815</t>
+          <t>51248</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>209656</t>
+          <t>76984</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>34,71%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>28,29%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>162653</t>
+          <t>118282</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>101620</t>
+          <t>98213</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>272424</t>
+          <t>141464</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>38,17%</t>
+          <t>30,25%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>36,18%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>128955</t>
+          <t>154452</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>113579</t>
+          <t>134685</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>139446</t>
+          <t>170315</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>77,04%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>64,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,31%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>134563</t>
+          <t>118263</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>49130</t>
+          <t>104160</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>192971</t>
+          <t>129896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>52,0%</t>
+          <t>65,29%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,57%</t>
+          <t>71,71%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>263518</t>
+          <t>272714</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>153747</t>
+          <t>249532</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>324551</t>
+          <t>292783</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>61,83%</t>
+          <t>69,75%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>36,08%</t>
+          <t>63,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>76,16%</t>
+          <t>74,88%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>167385</t>
+          <t>209852</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>167385</t>
+          <t>209852</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>167385</t>
+          <t>209852</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>258786</t>
+          <t>181144</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>258786</t>
+          <t>181144</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>258786</t>
+          <t>181144</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>426171</t>
+          <t>390996</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>426171</t>
+          <t>390996</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>426171</t>
+          <t>390996</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>50903</t>
+          <t>59482</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>41800</t>
+          <t>50308</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>59854</t>
+          <t>70520</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>52,39%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>62036</t>
+          <t>69313</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>54866</t>
+          <t>60654</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68535</t>
+          <t>77065</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>63,98%</t>
+          <t>64,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>112939</t>
+          <t>128795</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>101720</t>
+          <t>115945</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>124638</t>
+          <t>142490</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>51,02%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>56,31%</t>
+          <t>55,75%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>63336</t>
+          <t>76676</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>54385</t>
+          <t>65638</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72439</t>
+          <t>85850</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>56,31%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>47,61%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>63,41%</t>
+          <t>63,05%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>45081</t>
+          <t>50129</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>38582</t>
+          <t>42377</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>52251</t>
+          <t>58788</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,97%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,02%</t>
+          <t>35,48%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>49,22%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>108417</t>
+          <t>126805</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>96718</t>
+          <t>113110</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>119636</t>
+          <t>139655</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>48,98%</t>
+          <t>49,61%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>44,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,64%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>114239</t>
+          <t>136158</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>107117</t>
+          <t>119442</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>221356</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>221356</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>221356</t>
+          <t>255600</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2440,32 +2440,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>40305</t>
+          <t>40645</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>30078</t>
+          <t>31172</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50868</t>
+          <t>51095</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>29,84%</t>
+          <t>29,87%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,91%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,66%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,32 +2475,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>46510</t>
+          <t>47542</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>38490</t>
+          <t>40150</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>54008</t>
+          <t>55315</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,42%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>62,51%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,32 +2510,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>86815</t>
+          <t>88186</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74787</t>
+          <t>76121</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>99315</t>
+          <t>101359</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>39,2%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>33,77%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -2553,32 +2553,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>94756</t>
+          <t>95439</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>84193</t>
+          <t>84989</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>104983</t>
+          <t>104912</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>70,16%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,34%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,09%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,32 +2588,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>39892</t>
+          <t>39812</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>32394</t>
+          <t>32039</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47912</t>
+          <t>47204</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>46,17%</t>
+          <t>45,58%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>37,49%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,32 +2623,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>134648</t>
+          <t>135252</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>122148</t>
+          <t>122079</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>146676</t>
+          <t>147317</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,53%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,16%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,23%</t>
+          <t>65,93%</t>
         </is>
       </c>
     </row>
@@ -2666,17 +2666,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>135061</t>
+          <t>136084</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2701,17 +2701,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>86402</t>
+          <t>87354</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2736,17 +2736,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>221463</t>
+          <t>223438</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2783,32 +2783,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>37695</t>
+          <t>45936</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>26867</t>
+          <t>31741</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>52032</t>
+          <t>61594</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>11,28%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,32 +2818,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>74220</t>
+          <t>93290</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>62264</t>
+          <t>78835</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>88556</t>
+          <t>107727</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>21,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,32 +2853,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>111915</t>
+          <t>139226</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>94628</t>
+          <t>117013</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>132411</t>
+          <t>160716</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>18,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,62%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>20,66%</t>
+          <t>21,45%</t>
         </is>
       </c>
     </row>
@@ -2896,32 +2896,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>296556</t>
+          <t>341523</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>282219</t>
+          <t>325865</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>307384</t>
+          <t>355718</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>88,72%</t>
+          <t>88,14%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>91,81%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2931,32 +2931,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>232494</t>
+          <t>268557</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>218158</t>
+          <t>254120</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>244450</t>
+          <t>283012</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>74,22%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>78,21%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2966,32 +2966,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>529050</t>
+          <t>610079</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>508554</t>
+          <t>588589</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>546337</t>
+          <t>632292</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>82,54%</t>
+          <t>81,42%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>79,34%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>85,24%</t>
+          <t>84,38%</t>
         </is>
       </c>
     </row>
@@ -3009,17 +3009,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>334251</t>
+          <t>387459</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>334251</t>
+          <t>387459</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>334251</t>
+          <t>387459</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3044,17 +3044,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>306714</t>
+          <t>361847</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>306714</t>
+          <t>361847</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>306714</t>
+          <t>361847</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3079,17 +3079,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>640965</t>
+          <t>749305</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>640965</t>
+          <t>749305</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>640965</t>
+          <t>749305</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3126,32 +3126,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>117938</t>
+          <t>142286</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>41574</t>
+          <t>122298</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>202248</t>
+          <t>165563</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>36,39%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3161,32 +3161,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>128507</t>
+          <t>146676</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>113394</t>
+          <t>129405</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>143031</t>
+          <t>160657</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>47,4%</t>
+          <t>46,99%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,45%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>51,47%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3196,32 +3196,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>246445</t>
+          <t>288962</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>117820</t>
+          <t>261805</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>350445</t>
+          <t>316830</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>27,4%</t>
+          <t>37,67%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>38,96%</t>
+          <t>41,3%</t>
         </is>
       </c>
     </row>
@@ -3239,32 +3239,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>510387</t>
+          <t>312649</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>426077</t>
+          <t>289372</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>586751</t>
+          <t>332637</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>81,23%</t>
+          <t>68,72%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>93,38%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3274,32 +3274,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>142582</t>
+          <t>165489</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>128058</t>
+          <t>151508</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>157695</t>
+          <t>182760</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>52,6%</t>
+          <t>53,01%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>48,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,55%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3309,32 +3309,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>652969</t>
+          <t>478138</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>548969</t>
+          <t>450270</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>781594</t>
+          <t>505295</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>72,6%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,04%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>86,9%</t>
+          <t>65,87%</t>
         </is>
       </c>
     </row>
@@ -3352,17 +3352,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>628325</t>
+          <t>454935</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>271089</t>
+          <t>312165</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>271089</t>
+          <t>312165</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>271089</t>
+          <t>312165</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>899414</t>
+          <t>767100</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>899414</t>
+          <t>767100</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>899414</t>
+          <t>767100</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3469,32 +3469,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>407985</t>
+          <t>477078</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>274125</t>
+          <t>435206</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>478461</t>
+          <t>519577</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>13,95%</t>
+          <t>22,56%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3504,32 +3504,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>576256</t>
+          <t>570567</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>516941</t>
+          <t>537411</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>709865</t>
+          <t>603879</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>37,75%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3539,32 +3539,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>984242</t>
+          <t>1047645</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>808557</t>
+          <t>992323</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1142099</t>
+          <t>1098725</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>28,84%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>33,33%</t>
+          <t>31,94%</t>
         </is>
       </c>
     </row>
@@ -3582,32 +3582,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1557701</t>
+          <t>1452097</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1487225</t>
+          <t>1409598</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1691561</t>
+          <t>1493969</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>79,24%</t>
+          <t>75,27%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>86,05%</t>
+          <t>77,44%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3617,32 +3617,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>884679</t>
+          <t>940731</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>751070</t>
+          <t>907419</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>943994</t>
+          <t>973887</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>62,25%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,62%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3652,32 +3652,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>2442380</t>
+          <t>2392828</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>2284523</t>
+          <t>2341748</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>2618065</t>
+          <t>2448150</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>69,55%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>66,67%</t>
+          <t>68,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>71,16%</t>
         </is>
       </c>
     </row>
@@ -3695,17 +3695,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1965686</t>
+          <t>1929175</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3730,17 +3730,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>1460935</t>
+          <t>1511298</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3765,17 +3765,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>3426622</t>
+          <t>3440473</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
